--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -26393,14 +26393,14 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
-        <v>13268500</v>
+        <v>13197600</v>
       </c>
       <c r="I399" s="5" t="n">
-        <v>22004</v>
+        <v>21887</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
@@ -26408,10 +26408,10 @@
         </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>13268500</v>
+        <v>13197600</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>22004</v>
+        <v>21887</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -38629,14 +38629,14 @@
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H593" s="5" t="n">
-        <v>5270400</v>
+        <v>5416800</v>
       </c>
       <c r="I593" s="5" t="n">
-        <v>21082</v>
+        <v>21667</v>
       </c>
       <c r="J593" s="3" t="inlineStr">
         <is>
@@ -38644,10 +38644,10 @@
         </is>
       </c>
       <c r="K593" s="5" t="n">
-        <v>5270400</v>
+        <v>5416800</v>
       </c>
       <c r="L593" s="5" t="n">
-        <v>21082</v>
+        <v>21667</v>
       </c>
       <c r="M593" s="3" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
           <t>A | 936呎 (3房)
 $3184万
 $34,015/呎
-(26年-07月-07日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -51838,9 +51838,9 @@
       <c r="M12" s="21" t="inlineStr">
         <is>
           <t>M | 603呎 (2房)
-$1327万
-$22,004/呎
-(23年-07月-11日)</t>
+$1320万
+$21,887/呎
+(23年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -53470,9 +53470,9 @@
       <c r="K28" s="21" t="inlineStr">
         <is>
           <t>K | 250呎 (开放式)
-$527万
-$21,082/呎
-(23年-07月-11日)</t>
+$542万
+$21,667/呎
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -16868,38 +16868,30 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>31014000</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>33099</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K251" s="5" t="n">
+        <v>31014000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>33099</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16908,7 +16900,7 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -48057,7 +48049,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48067,7 +48059,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50211,12 +50203,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 937呎 (3房)
-招标单位
--
-(在售)</t>
+$3101万
+$33,099/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14731,14 +14731,14 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
         <v>30560000</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>32615</v>
+        <v>32650</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>30560000</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>32615</v>
+        <v>32650</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -15445,14 +15445,14 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
         <v>30513400</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>32565</v>
+        <v>32600</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>30513400</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>32565</v>
+        <v>32600</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -49920,10 +49920,10 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3056万
-$32,615/呎
-(26年-07月-27日)</t>
+$32,650/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -50015,10 +50015,10 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3051万
-$32,565/呎
-(26年-07月-27日)</t>
+$32,600/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -11,9 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N742"/>
+  <dimension ref="A1:N702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16159,7 +16157,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -44253,7 +44251,7 @@
     <row r="683">
       <c r="A683" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B683" s="3" t="inlineStr">
@@ -44281,14 +44279,14 @@
       </c>
       <c r="G683" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H683" s="5" t="n">
-        <v>6261300</v>
+        <v>6284200</v>
       </c>
       <c r="I683" s="5" t="n">
-        <v>20664</v>
+        <v>20740</v>
       </c>
       <c r="J683" s="3" t="inlineStr">
         <is>
@@ -44296,10 +44294,10 @@
         </is>
       </c>
       <c r="K683" s="5" t="n">
-        <v>6261300</v>
+        <v>6284200</v>
       </c>
       <c r="L683" s="5" t="n">
-        <v>20664</v>
+        <v>20740</v>
       </c>
       <c r="M683" s="3" t="inlineStr">
         <is>
@@ -44315,7 +44313,7 @@
     <row r="684">
       <c r="A684" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B684" s="3" t="inlineStr">
@@ -44343,14 +44341,14 @@
       </c>
       <c r="G684" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H684" s="5" t="n">
-        <v>6169500</v>
+        <v>6248500</v>
       </c>
       <c r="I684" s="5" t="n">
-        <v>20361</v>
+        <v>20622</v>
       </c>
       <c r="J684" s="3" t="inlineStr">
         <is>
@@ -44358,10 +44356,10 @@
         </is>
       </c>
       <c r="K684" s="5" t="n">
-        <v>6169500</v>
+        <v>6248500</v>
       </c>
       <c r="L684" s="5" t="n">
-        <v>20361</v>
+        <v>20622</v>
       </c>
       <c r="M684" s="3" t="inlineStr">
         <is>
@@ -44377,7 +44375,7 @@
     <row r="685">
       <c r="A685" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B685" s="3" t="inlineStr">
@@ -44405,14 +44403,14 @@
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="H685" s="5" t="n">
-        <v>14972100</v>
+        <v>13879800</v>
       </c>
       <c r="I685" s="5" t="n">
-        <v>23069</v>
+        <v>21386</v>
       </c>
       <c r="J685" s="3" t="inlineStr">
         <is>
@@ -44420,10 +44418,10 @@
         </is>
       </c>
       <c r="K685" s="5" t="n">
-        <v>14972100</v>
+        <v>13879800</v>
       </c>
       <c r="L685" s="5" t="n">
-        <v>23069</v>
+        <v>21386</v>
       </c>
       <c r="M685" s="3" t="inlineStr">
         <is>
@@ -44439,7 +44437,7 @@
     <row r="686">
       <c r="A686" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B686" s="3" t="inlineStr">
@@ -44458,7 +44456,7 @@
         </is>
       </c>
       <c r="E686" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F686" s="3" t="inlineStr">
         <is>
@@ -44467,14 +44465,14 @@
       </c>
       <c r="G686" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H686" s="5" t="n">
-        <v>15243400</v>
+        <v>14006800</v>
       </c>
       <c r="I686" s="5" t="n">
-        <v>23488</v>
+        <v>21615</v>
       </c>
       <c r="J686" s="3" t="inlineStr">
         <is>
@@ -44482,10 +44480,10 @@
         </is>
       </c>
       <c r="K686" s="5" t="n">
-        <v>15243400</v>
+        <v>14006800</v>
       </c>
       <c r="L686" s="5" t="n">
-        <v>23488</v>
+        <v>21615</v>
       </c>
       <c r="M686" s="3" t="inlineStr">
         <is>
@@ -44501,7 +44499,7 @@
     <row r="687">
       <c r="A687" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B687" s="3" t="inlineStr">
@@ -44529,14 +44527,14 @@
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="H687" s="5" t="n">
-        <v>6223500</v>
+        <v>13909300</v>
       </c>
       <c r="I687" s="5" t="n">
-        <v>20540</v>
+        <v>45905</v>
       </c>
       <c r="J687" s="3" t="inlineStr">
         <is>
@@ -44544,10 +44542,10 @@
         </is>
       </c>
       <c r="K687" s="5" t="n">
-        <v>6223500</v>
+        <v>13909300</v>
       </c>
       <c r="L687" s="5" t="n">
-        <v>20540</v>
+        <v>45905</v>
       </c>
       <c r="M687" s="3" t="inlineStr">
         <is>
@@ -44563,7 +44561,7 @@
     <row r="688">
       <c r="A688" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B688" s="3" t="inlineStr">
@@ -44582,7 +44580,7 @@
         </is>
       </c>
       <c r="E688" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F688" s="3" t="inlineStr">
         <is>
@@ -44591,14 +44589,14 @@
       </c>
       <c r="G688" s="3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H688" s="5" t="n">
-        <v>6624000</v>
+        <v>6109200</v>
       </c>
       <c r="I688" s="5" t="n">
-        <v>21861</v>
+        <v>20096</v>
       </c>
       <c r="J688" s="3" t="inlineStr">
         <is>
@@ -44606,10 +44604,10 @@
         </is>
       </c>
       <c r="K688" s="5" t="n">
-        <v>6624000</v>
+        <v>6109200</v>
       </c>
       <c r="L688" s="5" t="n">
-        <v>21861</v>
+        <v>20096</v>
       </c>
       <c r="M688" s="3" t="inlineStr">
         <is>
@@ -44625,7 +44623,7 @@
     <row r="689">
       <c r="A689" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B689" s="3" t="inlineStr">
@@ -44653,14 +44651,14 @@
       </c>
       <c r="G689" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="H689" s="5" t="n">
-        <v>14621700</v>
+        <v>13909300</v>
       </c>
       <c r="I689" s="5" t="n">
-        <v>22530</v>
+        <v>21432</v>
       </c>
       <c r="J689" s="3" t="inlineStr">
         <is>
@@ -44668,10 +44666,10 @@
         </is>
       </c>
       <c r="K689" s="5" t="n">
-        <v>14621700</v>
+        <v>13909300</v>
       </c>
       <c r="L689" s="5" t="n">
-        <v>22530</v>
+        <v>21432</v>
       </c>
       <c r="M689" s="3" t="inlineStr">
         <is>
@@ -44687,7 +44685,7 @@
     <row r="690">
       <c r="A690" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B690" s="3" t="inlineStr">
@@ -44706,7 +44704,7 @@
         </is>
       </c>
       <c r="E690" s="4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F690" s="3" t="inlineStr">
         <is>
@@ -44715,14 +44713,14 @@
       </c>
       <c r="G690" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="H690" s="5" t="n">
-        <v>14810100</v>
+        <v>13808300</v>
       </c>
       <c r="I690" s="5" t="n">
-        <v>22820</v>
+        <v>21309</v>
       </c>
       <c r="J690" s="3" t="inlineStr">
         <is>
@@ -44730,10 +44728,10 @@
         </is>
       </c>
       <c r="K690" s="5" t="n">
-        <v>14810100</v>
+        <v>13808300</v>
       </c>
       <c r="L690" s="5" t="n">
-        <v>22820</v>
+        <v>21309</v>
       </c>
       <c r="M690" s="3" t="inlineStr">
         <is>
@@ -44749,7 +44747,7 @@
     <row r="691">
       <c r="A691" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B691" s="3" t="inlineStr">
@@ -44768,7 +44766,7 @@
         </is>
       </c>
       <c r="E691" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F691" s="3" t="inlineStr">
         <is>
@@ -44777,14 +44775,14 @@
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H691" s="5" t="n">
-        <v>6185700</v>
+        <v>6108300</v>
       </c>
       <c r="I691" s="5" t="n">
-        <v>20415</v>
+        <v>20093</v>
       </c>
       <c r="J691" s="3" t="inlineStr">
         <is>
@@ -44792,10 +44790,10 @@
         </is>
       </c>
       <c r="K691" s="5" t="n">
-        <v>6185700</v>
+        <v>6108300</v>
       </c>
       <c r="L691" s="5" t="n">
-        <v>20415</v>
+        <v>20093</v>
       </c>
       <c r="M691" s="3" t="inlineStr">
         <is>
@@ -44811,7 +44809,7 @@
     <row r="692">
       <c r="A692" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B692" s="3" t="inlineStr">
@@ -44830,7 +44828,7 @@
         </is>
       </c>
       <c r="E692" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F692" s="3" t="inlineStr">
         <is>
@@ -44839,14 +44837,14 @@
       </c>
       <c r="G692" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H692" s="5" t="n">
-        <v>6199100</v>
+        <v>6173500</v>
       </c>
       <c r="I692" s="5" t="n">
-        <v>20459</v>
+        <v>20308</v>
       </c>
       <c r="J692" s="3" t="inlineStr">
         <is>
@@ -44854,10 +44852,10 @@
         </is>
       </c>
       <c r="K692" s="5" t="n">
-        <v>6199100</v>
+        <v>6173500</v>
       </c>
       <c r="L692" s="5" t="n">
-        <v>20459</v>
+        <v>20308</v>
       </c>
       <c r="M692" s="3" t="inlineStr">
         <is>
@@ -44873,7 +44871,7 @@
     <row r="693">
       <c r="A693" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B693" s="3" t="inlineStr">
@@ -44901,14 +44899,14 @@
       </c>
       <c r="G693" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H693" s="5" t="n">
-        <v>14446900</v>
+        <v>13901500</v>
       </c>
       <c r="I693" s="5" t="n">
-        <v>22260</v>
+        <v>21420</v>
       </c>
       <c r="J693" s="3" t="inlineStr">
         <is>
@@ -44916,10 +44914,10 @@
         </is>
       </c>
       <c r="K693" s="5" t="n">
-        <v>14446900</v>
+        <v>13901500</v>
       </c>
       <c r="L693" s="5" t="n">
-        <v>22260</v>
+        <v>21420</v>
       </c>
       <c r="M693" s="3" t="inlineStr">
         <is>
@@ -44935,7 +44933,7 @@
     <row r="694">
       <c r="A694" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B694" s="3" t="inlineStr">
@@ -44963,14 +44961,14 @@
       </c>
       <c r="G694" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H694" s="5" t="n">
-        <v>14395500</v>
+        <v>13801800</v>
       </c>
       <c r="I694" s="5" t="n">
-        <v>22215</v>
+        <v>21299</v>
       </c>
       <c r="J694" s="3" t="inlineStr">
         <is>
@@ -44978,10 +44976,10 @@
         </is>
       </c>
       <c r="K694" s="5" t="n">
-        <v>14395500</v>
+        <v>13801800</v>
       </c>
       <c r="L694" s="5" t="n">
-        <v>22215</v>
+        <v>21299</v>
       </c>
       <c r="M694" s="3" t="inlineStr">
         <is>
@@ -44997,7 +44995,7 @@
     <row r="695">
       <c r="A695" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B695" s="3" t="inlineStr">
@@ -45029,10 +45027,10 @@
         </is>
       </c>
       <c r="H695" s="5" t="n">
-        <v>6147900</v>
+        <v>6071400</v>
       </c>
       <c r="I695" s="5" t="n">
-        <v>20223</v>
+        <v>19972</v>
       </c>
       <c r="J695" s="3" t="inlineStr">
         <is>
@@ -45040,10 +45038,10 @@
         </is>
       </c>
       <c r="K695" s="5" t="n">
-        <v>6147900</v>
+        <v>6071400</v>
       </c>
       <c r="L695" s="5" t="n">
-        <v>20223</v>
+        <v>19972</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -45059,7 +45057,7 @@
     <row r="696">
       <c r="A696" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B696" s="3" t="inlineStr">
@@ -45078,7 +45076,7 @@
         </is>
       </c>
       <c r="E696" s="4" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
@@ -45087,14 +45085,14 @@
       </c>
       <c r="G696" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H696" s="5" t="n">
-        <v>6061500</v>
+        <v>6102400</v>
       </c>
       <c r="I696" s="5" t="n">
-        <v>20005</v>
+        <v>20074</v>
       </c>
       <c r="J696" s="3" t="inlineStr">
         <is>
@@ -45102,10 +45100,10 @@
         </is>
       </c>
       <c r="K696" s="5" t="n">
-        <v>6061500</v>
+        <v>6102400</v>
       </c>
       <c r="L696" s="5" t="n">
-        <v>20005</v>
+        <v>20074</v>
       </c>
       <c r="M696" s="3" t="inlineStr">
         <is>
@@ -45121,7 +45119,7 @@
     <row r="697">
       <c r="A697" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B697" s="3" t="inlineStr">
@@ -45149,14 +45147,14 @@
       </c>
       <c r="G697" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H697" s="5" t="n">
-        <v>14428100</v>
+        <v>13591800</v>
       </c>
       <c r="I697" s="5" t="n">
-        <v>22266</v>
+        <v>20975</v>
       </c>
       <c r="J697" s="3" t="inlineStr">
         <is>
@@ -45164,10 +45162,10 @@
         </is>
       </c>
       <c r="K697" s="5" t="n">
-        <v>14428100</v>
+        <v>13591800</v>
       </c>
       <c r="L697" s="5" t="n">
-        <v>22266</v>
+        <v>20975</v>
       </c>
       <c r="M697" s="3" t="inlineStr">
         <is>
@@ -45183,7 +45181,7 @@
     <row r="698">
       <c r="A698" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B698" s="3" t="inlineStr">
@@ -45211,14 +45209,14 @@
       </c>
       <c r="G698" s="3" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H698" s="5" t="n">
-        <v>14223600</v>
+        <v>13720400</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>21916</v>
+        <v>21141</v>
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
@@ -45226,10 +45224,10 @@
         </is>
       </c>
       <c r="K698" s="5" t="n">
-        <v>14223600</v>
+        <v>13720400</v>
       </c>
       <c r="L698" s="5" t="n">
-        <v>21916</v>
+        <v>21141</v>
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
@@ -45245,7 +45243,7 @@
     <row r="699">
       <c r="A699" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B699" s="3" t="inlineStr">
@@ -45273,14 +45271,14 @@
       </c>
       <c r="G699" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H699" s="5" t="n">
-        <v>6581500</v>
+        <v>6719200</v>
       </c>
       <c r="I699" s="5" t="n">
-        <v>23339</v>
+        <v>23827</v>
       </c>
       <c r="J699" s="3" t="inlineStr">
         <is>
@@ -45288,10 +45286,10 @@
         </is>
       </c>
       <c r="K699" s="5" t="n">
-        <v>6581500</v>
+        <v>6719200</v>
       </c>
       <c r="L699" s="5" t="n">
-        <v>23339</v>
+        <v>23827</v>
       </c>
       <c r="M699" s="3" t="inlineStr">
         <is>
@@ -45307,7 +45305,7 @@
     <row r="700">
       <c r="A700" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B700" s="3" t="inlineStr">
@@ -45335,14 +45333,14 @@
       </c>
       <c r="G700" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H700" s="5" t="n">
-        <v>6560100</v>
+        <v>6608100</v>
       </c>
       <c r="I700" s="5" t="n">
-        <v>23263</v>
+        <v>23433</v>
       </c>
       <c r="J700" s="3" t="inlineStr">
         <is>
@@ -45350,10 +45348,10 @@
         </is>
       </c>
       <c r="K700" s="5" t="n">
-        <v>6560100</v>
+        <v>6608100</v>
       </c>
       <c r="L700" s="5" t="n">
-        <v>23263</v>
+        <v>23433</v>
       </c>
       <c r="M700" s="3" t="inlineStr">
         <is>
@@ -45369,7 +45367,7 @@
     <row r="701">
       <c r="A701" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B701" s="3" t="inlineStr">
@@ -45388,7 +45386,7 @@
         </is>
       </c>
       <c r="E701" s="4" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
@@ -45397,14 +45395,14 @@
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
-        <v>17241300</v>
+        <v>16854300</v>
       </c>
       <c r="I701" s="5" t="n">
-        <v>27498</v>
+        <v>26924</v>
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
@@ -45412,10 +45410,10 @@
         </is>
       </c>
       <c r="K701" s="5" t="n">
-        <v>17241300</v>
+        <v>16854300</v>
       </c>
       <c r="L701" s="5" t="n">
-        <v>27498</v>
+        <v>26924</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
@@ -45431,7 +45429,7 @@
     <row r="702">
       <c r="A702" s="3" t="inlineStr">
         <is>
-          <t>低座B座</t>
+          <t>低座D座</t>
         </is>
       </c>
       <c r="B702" s="3" t="inlineStr">
@@ -45459,14 +45457,14 @@
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H702" s="5" t="n">
-        <v>17109900</v>
+        <v>16816700</v>
       </c>
       <c r="I702" s="5" t="n">
-        <v>27289</v>
+        <v>26821</v>
       </c>
       <c r="J702" s="3" t="inlineStr">
         <is>
@@ -45474,10 +45472,10 @@
         </is>
       </c>
       <c r="K702" s="5" t="n">
-        <v>17109900</v>
+        <v>16816700</v>
       </c>
       <c r="L702" s="5" t="n">
-        <v>27289</v>
+        <v>26821</v>
       </c>
       <c r="M702" s="3" t="inlineStr">
         <is>
@@ -45485,2486 +45483,6 @@
         </is>
       </c>
       <c r="N702" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B703" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C703" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D703" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E703" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F703" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G703" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H703" s="5" t="n">
-        <v>6637500</v>
-      </c>
-      <c r="I703" s="5" t="n">
-        <v>21834</v>
-      </c>
-      <c r="J703" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K703" s="5" t="n">
-        <v>6637500</v>
-      </c>
-      <c r="L703" s="5" t="n">
-        <v>21834</v>
-      </c>
-      <c r="M703" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N703" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B704" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C704" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D704" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E704" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F704" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G704" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H704" s="5" t="n">
-        <v>6566400</v>
-      </c>
-      <c r="I704" s="5" t="n">
-        <v>21671</v>
-      </c>
-      <c r="J704" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K704" s="5" t="n">
-        <v>6566400</v>
-      </c>
-      <c r="L704" s="5" t="n">
-        <v>21671</v>
-      </c>
-      <c r="M704" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N704" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B705" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C705" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D705" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E705" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F705" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G705" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H705" s="5" t="n">
-        <v>14935500</v>
-      </c>
-      <c r="I705" s="5" t="n">
-        <v>23049</v>
-      </c>
-      <c r="J705" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K705" s="5" t="n">
-        <v>14935500</v>
-      </c>
-      <c r="L705" s="5" t="n">
-        <v>23049</v>
-      </c>
-      <c r="M705" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N705" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B706" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C706" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D706" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E706" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F706" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G706" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="H706" s="5" t="n">
-        <v>15207000</v>
-      </c>
-      <c r="I706" s="5" t="n">
-        <v>23468</v>
-      </c>
-      <c r="J706" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K706" s="5" t="n">
-        <v>15207000</v>
-      </c>
-      <c r="L706" s="5" t="n">
-        <v>23468</v>
-      </c>
-      <c r="M706" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N706" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B707" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C707" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D707" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E707" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F707" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G707" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H707" s="5" t="n">
-        <v>6597900</v>
-      </c>
-      <c r="I707" s="5" t="n">
-        <v>21775</v>
-      </c>
-      <c r="J707" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K707" s="5" t="n">
-        <v>6597900</v>
-      </c>
-      <c r="L707" s="5" t="n">
-        <v>21775</v>
-      </c>
-      <c r="M707" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N707" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B708" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C708" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D708" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E708" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F708" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G708" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H708" s="5" t="n">
-        <v>6599300</v>
-      </c>
-      <c r="I708" s="5" t="n">
-        <v>21708</v>
-      </c>
-      <c r="J708" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K708" s="5" t="n">
-        <v>6599300</v>
-      </c>
-      <c r="L708" s="5" t="n">
-        <v>21708</v>
-      </c>
-      <c r="M708" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N708" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B709" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C709" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D709" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E709" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F709" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G709" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="H709" s="5" t="n">
-        <v>14803200</v>
-      </c>
-      <c r="I709" s="5" t="n">
-        <v>22809</v>
-      </c>
-      <c r="J709" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K709" s="5" t="n">
-        <v>14803200</v>
-      </c>
-      <c r="L709" s="5" t="n">
-        <v>22809</v>
-      </c>
-      <c r="M709" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N709" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B710" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C710" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D710" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E710" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F710" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G710" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H710" s="5" t="n">
-        <v>14907600</v>
-      </c>
-      <c r="I710" s="5" t="n">
-        <v>23006</v>
-      </c>
-      <c r="J710" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K710" s="5" t="n">
-        <v>14907600</v>
-      </c>
-      <c r="L710" s="5" t="n">
-        <v>23006</v>
-      </c>
-      <c r="M710" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N710" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B711" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C711" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D711" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E711" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F711" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G711" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H711" s="5" t="n">
-        <v>6741400</v>
-      </c>
-      <c r="I711" s="5" t="n">
-        <v>22176</v>
-      </c>
-      <c r="J711" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K711" s="5" t="n">
-        <v>6741400</v>
-      </c>
-      <c r="L711" s="5" t="n">
-        <v>22176</v>
-      </c>
-      <c r="M711" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N711" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B712" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C712" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D712" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E712" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F712" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G712" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H712" s="5" t="n">
-        <v>6596200</v>
-      </c>
-      <c r="I712" s="5" t="n">
-        <v>21698</v>
-      </c>
-      <c r="J712" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K712" s="5" t="n">
-        <v>6596200</v>
-      </c>
-      <c r="L712" s="5" t="n">
-        <v>21698</v>
-      </c>
-      <c r="M712" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N712" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B713" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C713" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D713" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E713" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F713" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G713" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="H713" s="5" t="n">
-        <v>14715000</v>
-      </c>
-      <c r="I713" s="5" t="n">
-        <v>22673</v>
-      </c>
-      <c r="J713" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K713" s="5" t="n">
-        <v>14715000</v>
-      </c>
-      <c r="L713" s="5" t="n">
-        <v>22673</v>
-      </c>
-      <c r="M713" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N713" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B714" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C714" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D714" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E714" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F714" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G714" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="H714" s="5" t="n">
-        <v>14820300</v>
-      </c>
-      <c r="I714" s="5" t="n">
-        <v>22836</v>
-      </c>
-      <c r="J714" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K714" s="5" t="n">
-        <v>14820300</v>
-      </c>
-      <c r="L714" s="5" t="n">
-        <v>22836</v>
-      </c>
-      <c r="M714" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N714" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B715" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C715" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D715" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E715" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F715" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G715" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="H715" s="5" t="n">
-        <v>6519600</v>
-      </c>
-      <c r="I715" s="5" t="n">
-        <v>21446</v>
-      </c>
-      <c r="J715" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K715" s="5" t="n">
-        <v>6519600</v>
-      </c>
-      <c r="L715" s="5" t="n">
-        <v>21446</v>
-      </c>
-      <c r="M715" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N715" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B716" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C716" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D716" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E716" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F716" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G716" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="H716" s="5" t="n">
-        <v>6448500</v>
-      </c>
-      <c r="I716" s="5" t="n">
-        <v>21212</v>
-      </c>
-      <c r="J716" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K716" s="5" t="n">
-        <v>6448500</v>
-      </c>
-      <c r="L716" s="5" t="n">
-        <v>21212</v>
-      </c>
-      <c r="M716" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N716" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B717" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C717" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D717" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E717" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F717" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G717" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="H717" s="5" t="n">
-        <v>14789300</v>
-      </c>
-      <c r="I717" s="5" t="n">
-        <v>22788</v>
-      </c>
-      <c r="J717" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K717" s="5" t="n">
-        <v>14789300</v>
-      </c>
-      <c r="L717" s="5" t="n">
-        <v>22788</v>
-      </c>
-      <c r="M717" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N717" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B718" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C718" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D718" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E718" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F718" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G718" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H718" s="5" t="n">
-        <v>14732100</v>
-      </c>
-      <c r="I718" s="5" t="n">
-        <v>22700</v>
-      </c>
-      <c r="J718" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K718" s="5" t="n">
-        <v>14732100</v>
-      </c>
-      <c r="L718" s="5" t="n">
-        <v>22700</v>
-      </c>
-      <c r="M718" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N718" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B719" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C719" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D719" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E719" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F719" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G719" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="H719" s="5" t="n">
-        <v>6885000</v>
-      </c>
-      <c r="I719" s="5" t="n">
-        <v>24415</v>
-      </c>
-      <c r="J719" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K719" s="5" t="n">
-        <v>6885000</v>
-      </c>
-      <c r="L719" s="5" t="n">
-        <v>24415</v>
-      </c>
-      <c r="M719" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N719" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B720" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C720" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D720" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E720" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F720" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G720" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="H720" s="5" t="n">
-        <v>6809400</v>
-      </c>
-      <c r="I720" s="5" t="n">
-        <v>24147</v>
-      </c>
-      <c r="J720" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K720" s="5" t="n">
-        <v>6809400</v>
-      </c>
-      <c r="L720" s="5" t="n">
-        <v>24147</v>
-      </c>
-      <c r="M720" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N720" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B721" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C721" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D721" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E721" s="4" t="n">
-        <v>627</v>
-      </c>
-      <c r="F721" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G721" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H721" s="5" t="n">
-        <v>17827800</v>
-      </c>
-      <c r="I721" s="5" t="n">
-        <v>28433</v>
-      </c>
-      <c r="J721" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K721" s="5" t="n">
-        <v>17827800</v>
-      </c>
-      <c r="L721" s="5" t="n">
-        <v>28433</v>
-      </c>
-      <c r="M721" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N721" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" s="3" t="inlineStr">
-        <is>
-          <t>低座C座</t>
-        </is>
-      </c>
-      <c r="B722" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C722" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D722" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E722" s="4" t="n">
-        <v>627</v>
-      </c>
-      <c r="F722" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G722" s="3" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="H722" s="5" t="n">
-        <v>17585100</v>
-      </c>
-      <c r="I722" s="5" t="n">
-        <v>28046</v>
-      </c>
-      <c r="J722" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K722" s="5" t="n">
-        <v>17585100</v>
-      </c>
-      <c r="L722" s="5" t="n">
-        <v>28046</v>
-      </c>
-      <c r="M722" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N722" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B723" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C723" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D723" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E723" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F723" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G723" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H723" s="5" t="n">
-        <v>6284200</v>
-      </c>
-      <c r="I723" s="5" t="n">
-        <v>20740</v>
-      </c>
-      <c r="J723" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K723" s="5" t="n">
-        <v>6284200</v>
-      </c>
-      <c r="L723" s="5" t="n">
-        <v>20740</v>
-      </c>
-      <c r="M723" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N723" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B724" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C724" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D724" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E724" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F724" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G724" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H724" s="5" t="n">
-        <v>6248500</v>
-      </c>
-      <c r="I724" s="5" t="n">
-        <v>20622</v>
-      </c>
-      <c r="J724" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K724" s="5" t="n">
-        <v>6248500</v>
-      </c>
-      <c r="L724" s="5" t="n">
-        <v>20622</v>
-      </c>
-      <c r="M724" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N724" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B725" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C725" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D725" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E725" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F725" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G725" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-21</t>
-        </is>
-      </c>
-      <c r="H725" s="5" t="n">
-        <v>13879800</v>
-      </c>
-      <c r="I725" s="5" t="n">
-        <v>21386</v>
-      </c>
-      <c r="J725" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K725" s="5" t="n">
-        <v>13879800</v>
-      </c>
-      <c r="L725" s="5" t="n">
-        <v>21386</v>
-      </c>
-      <c r="M725" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N725" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B726" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C726" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D726" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E726" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F726" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G726" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H726" s="5" t="n">
-        <v>14006800</v>
-      </c>
-      <c r="I726" s="5" t="n">
-        <v>21615</v>
-      </c>
-      <c r="J726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K726" s="5" t="n">
-        <v>14006800</v>
-      </c>
-      <c r="L726" s="5" t="n">
-        <v>21615</v>
-      </c>
-      <c r="M726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N726" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B727" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C727" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D727" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E727" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="F727" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G727" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="H727" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="I727" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="J727" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K727" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="L727" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="M727" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N727" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B728" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C728" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D728" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E728" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F728" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G728" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H728" s="5" t="n">
-        <v>6109200</v>
-      </c>
-      <c r="I728" s="5" t="n">
-        <v>20096</v>
-      </c>
-      <c r="J728" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K728" s="5" t="n">
-        <v>6109200</v>
-      </c>
-      <c r="L728" s="5" t="n">
-        <v>20096</v>
-      </c>
-      <c r="M728" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N728" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B729" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C729" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D729" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E729" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F729" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G729" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="H729" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="I729" s="5" t="n">
-        <v>21432</v>
-      </c>
-      <c r="J729" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K729" s="5" t="n">
-        <v>13909300</v>
-      </c>
-      <c r="L729" s="5" t="n">
-        <v>21432</v>
-      </c>
-      <c r="M729" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N729" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B730" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C730" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D730" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E730" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F730" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G730" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="H730" s="5" t="n">
-        <v>13808300</v>
-      </c>
-      <c r="I730" s="5" t="n">
-        <v>21309</v>
-      </c>
-      <c r="J730" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K730" s="5" t="n">
-        <v>13808300</v>
-      </c>
-      <c r="L730" s="5" t="n">
-        <v>21309</v>
-      </c>
-      <c r="M730" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N730" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B731" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D731" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E731" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F731" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G731" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-26</t>
-        </is>
-      </c>
-      <c r="H731" s="5" t="n">
-        <v>6108300</v>
-      </c>
-      <c r="I731" s="5" t="n">
-        <v>20093</v>
-      </c>
-      <c r="J731" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K731" s="5" t="n">
-        <v>6108300</v>
-      </c>
-      <c r="L731" s="5" t="n">
-        <v>20093</v>
-      </c>
-      <c r="M731" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N731" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B732" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C732" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D732" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E732" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F732" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G732" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H732" s="5" t="n">
-        <v>6173500</v>
-      </c>
-      <c r="I732" s="5" t="n">
-        <v>20308</v>
-      </c>
-      <c r="J732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K732" s="5" t="n">
-        <v>6173500</v>
-      </c>
-      <c r="L732" s="5" t="n">
-        <v>20308</v>
-      </c>
-      <c r="M732" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N732" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B733" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C733" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D733" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E733" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F733" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G733" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H733" s="5" t="n">
-        <v>13901500</v>
-      </c>
-      <c r="I733" s="5" t="n">
-        <v>21420</v>
-      </c>
-      <c r="J733" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K733" s="5" t="n">
-        <v>13901500</v>
-      </c>
-      <c r="L733" s="5" t="n">
-        <v>21420</v>
-      </c>
-      <c r="M733" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N733" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B734" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C734" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D734" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E734" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F734" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G734" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H734" s="5" t="n">
-        <v>13801800</v>
-      </c>
-      <c r="I734" s="5" t="n">
-        <v>21299</v>
-      </c>
-      <c r="J734" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K734" s="5" t="n">
-        <v>13801800</v>
-      </c>
-      <c r="L734" s="5" t="n">
-        <v>21299</v>
-      </c>
-      <c r="M734" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N734" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B735" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C735" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D735" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E735" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F735" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G735" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-21</t>
-        </is>
-      </c>
-      <c r="H735" s="5" t="n">
-        <v>6071400</v>
-      </c>
-      <c r="I735" s="5" t="n">
-        <v>19972</v>
-      </c>
-      <c r="J735" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K735" s="5" t="n">
-        <v>6071400</v>
-      </c>
-      <c r="L735" s="5" t="n">
-        <v>19972</v>
-      </c>
-      <c r="M735" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N735" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B736" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C736" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D736" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E736" s="4" t="n">
-        <v>304</v>
-      </c>
-      <c r="F736" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G736" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H736" s="5" t="n">
-        <v>6102400</v>
-      </c>
-      <c r="I736" s="5" t="n">
-        <v>20074</v>
-      </c>
-      <c r="J736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K736" s="5" t="n">
-        <v>6102400</v>
-      </c>
-      <c r="L736" s="5" t="n">
-        <v>20074</v>
-      </c>
-      <c r="M736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N736" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B737" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C737" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D737" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E737" s="4" t="n">
-        <v>648</v>
-      </c>
-      <c r="F737" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G737" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="H737" s="5" t="n">
-        <v>13591800</v>
-      </c>
-      <c r="I737" s="5" t="n">
-        <v>20975</v>
-      </c>
-      <c r="J737" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K737" s="5" t="n">
-        <v>13591800</v>
-      </c>
-      <c r="L737" s="5" t="n">
-        <v>20975</v>
-      </c>
-      <c r="M737" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N737" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B738" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C738" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D738" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E738" s="4" t="n">
-        <v>649</v>
-      </c>
-      <c r="F738" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G738" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="H738" s="5" t="n">
-        <v>13720400</v>
-      </c>
-      <c r="I738" s="5" t="n">
-        <v>21141</v>
-      </c>
-      <c r="J738" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K738" s="5" t="n">
-        <v>13720400</v>
-      </c>
-      <c r="L738" s="5" t="n">
-        <v>21141</v>
-      </c>
-      <c r="M738" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N738" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B739" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C739" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D739" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E739" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F739" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G739" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H739" s="5" t="n">
-        <v>6719200</v>
-      </c>
-      <c r="I739" s="5" t="n">
-        <v>23827</v>
-      </c>
-      <c r="J739" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K739" s="5" t="n">
-        <v>6719200</v>
-      </c>
-      <c r="L739" s="5" t="n">
-        <v>23827</v>
-      </c>
-      <c r="M739" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N739" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B740" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C740" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D740" s="3" t="inlineStr">
-        <is>
-          <t>1房</t>
-        </is>
-      </c>
-      <c r="E740" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F740" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G740" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H740" s="5" t="n">
-        <v>6608100</v>
-      </c>
-      <c r="I740" s="5" t="n">
-        <v>23433</v>
-      </c>
-      <c r="J740" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K740" s="5" t="n">
-        <v>6608100</v>
-      </c>
-      <c r="L740" s="5" t="n">
-        <v>23433</v>
-      </c>
-      <c r="M740" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N740" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B741" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C741" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D741" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E741" s="4" t="n">
-        <v>626</v>
-      </c>
-      <c r="F741" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G741" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="H741" s="5" t="n">
-        <v>16854300</v>
-      </c>
-      <c r="I741" s="5" t="n">
-        <v>26924</v>
-      </c>
-      <c r="J741" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K741" s="5" t="n">
-        <v>16854300</v>
-      </c>
-      <c r="L741" s="5" t="n">
-        <v>26924</v>
-      </c>
-      <c r="M741" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N741" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" s="3" t="inlineStr">
-        <is>
-          <t>低座D座</t>
-        </is>
-      </c>
-      <c r="B742" s="3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C742" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D742" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E742" s="4" t="n">
-        <v>627</v>
-      </c>
-      <c r="F742" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G742" s="3" t="inlineStr">
-        <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="H742" s="5" t="n">
-        <v>16816700</v>
-      </c>
-      <c r="I742" s="5" t="n">
-        <v>26821</v>
-      </c>
-      <c r="J742" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K742" s="5" t="n">
-        <v>16816700</v>
-      </c>
-      <c r="L742" s="5" t="n">
-        <v>26821</v>
-      </c>
-      <c r="M742" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N742" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -50113,7 +47631,7 @@
           <t>A | 936呎 (3房)
 $3111万
 $33,237/呎
-(26年-07月-27日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -54345,642 +51863,6 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>低座B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1524万
-$23,488/呎
-(23年-07月-19日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1497万
-$23,069/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$617万
-$20,361/呎
-(23年-07月-18日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 303呎 (1房)
-$626万
-$20,664/呎
-(23年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1481万
-$22,820/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1462万
-$22,530/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$662万
-$21,861/呎
-(23年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 303呎 (1房)
-$622万
-$20,540/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 648呎 (3房)
-$1440万
-$22,215/呎
-(23年-07月-19日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1445万
-$22,260/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$620万
-$20,459/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 303呎 (1房)
-$619万
-$20,415/呎
-(23年-07月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1422万
-$21,916/呎
-(23年-08月-04日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 648呎 (3房)
-$1443万
-$22,266/呎
-(23年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$606万
-$20,005/呎
-(23年-07月-25日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$615万
-$20,223/呎
-(23年-07月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 627呎 (3房)
-$1711万
-$27,289/呎
-(23年-07月-25日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 627呎 (3房)
-$1724万
-$27,498/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$656万
-$23,263/呎
-(23年-07月-26日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 282呎 (1房)
-$658万
-$23,339/呎
-(23年-07月-25日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>低座C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 648呎 (3房)
-$1521万
-$23,468/呎
-(23年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 648呎 (3房)
-$1494万
-$23,049/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 303呎 (1房)
-$657万
-$21,671/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$664万
-$21,834/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 648呎 (3房)
-$1491万
-$23,006/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1480万
-$22,809/呎
-(23年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$660万
-$21,708/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 303呎 (1房)
-$660万
-$21,775/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1482万
-$22,836/呎
-(23年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1472万
-$22,673/呎
-(23年-08月-04日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$660万
-$21,698/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$674万
-$22,176/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 649呎 (3房)
-$1473万
-$22,700/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 649呎 (3房)
-$1479万
-$22,788/呎
-(23年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 304呎 (1房)
-$645万
-$21,212/呎
-(23年-08月-07日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>D | 304呎 (1房)
-$652万
-$21,446/呎
-(23年-07月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 627呎 (3房)
-$1759万
-$28,046/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 627呎 (3房)
-$1783万
-$28,433/呎
-(23年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 282呎 (1房)
-$681万
-$24,147/呎
-(23年-08月-01日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 282呎 (1房)
-$688万
-$24,415/呎
-(23年-07月-31日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
           <t>低座D座 销控网格图</t>
         </is>
       </c>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -654,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N702"/>
+  <dimension ref="A1:N742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -44251,7 +44253,7 @@
     <row r="683">
       <c r="A683" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B683" s="3" t="inlineStr">
@@ -44279,14 +44281,14 @@
       </c>
       <c r="G683" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H683" s="5" t="n">
-        <v>6284200</v>
+        <v>6261300</v>
       </c>
       <c r="I683" s="5" t="n">
-        <v>20740</v>
+        <v>20664</v>
       </c>
       <c r="J683" s="3" t="inlineStr">
         <is>
@@ -44294,10 +44296,10 @@
         </is>
       </c>
       <c r="K683" s="5" t="n">
-        <v>6284200</v>
+        <v>6261300</v>
       </c>
       <c r="L683" s="5" t="n">
-        <v>20740</v>
+        <v>20664</v>
       </c>
       <c r="M683" s="3" t="inlineStr">
         <is>
@@ -44313,7 +44315,7 @@
     <row r="684">
       <c r="A684" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B684" s="3" t="inlineStr">
@@ -44341,14 +44343,14 @@
       </c>
       <c r="G684" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H684" s="5" t="n">
-        <v>6248500</v>
+        <v>6169500</v>
       </c>
       <c r="I684" s="5" t="n">
-        <v>20622</v>
+        <v>20361</v>
       </c>
       <c r="J684" s="3" t="inlineStr">
         <is>
@@ -44356,10 +44358,10 @@
         </is>
       </c>
       <c r="K684" s="5" t="n">
-        <v>6248500</v>
+        <v>6169500</v>
       </c>
       <c r="L684" s="5" t="n">
-        <v>20622</v>
+        <v>20361</v>
       </c>
       <c r="M684" s="3" t="inlineStr">
         <is>
@@ -44375,7 +44377,7 @@
     <row r="685">
       <c r="A685" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B685" s="3" t="inlineStr">
@@ -44403,14 +44405,14 @@
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H685" s="5" t="n">
-        <v>13879800</v>
+        <v>14972100</v>
       </c>
       <c r="I685" s="5" t="n">
-        <v>21386</v>
+        <v>23069</v>
       </c>
       <c r="J685" s="3" t="inlineStr">
         <is>
@@ -44418,10 +44420,10 @@
         </is>
       </c>
       <c r="K685" s="5" t="n">
-        <v>13879800</v>
+        <v>14972100</v>
       </c>
       <c r="L685" s="5" t="n">
-        <v>21386</v>
+        <v>23069</v>
       </c>
       <c r="M685" s="3" t="inlineStr">
         <is>
@@ -44437,7 +44439,7 @@
     <row r="686">
       <c r="A686" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B686" s="3" t="inlineStr">
@@ -44456,7 +44458,7 @@
         </is>
       </c>
       <c r="E686" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F686" s="3" t="inlineStr">
         <is>
@@ -44465,14 +44467,14 @@
       </c>
       <c r="G686" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H686" s="5" t="n">
-        <v>14006800</v>
+        <v>15243400</v>
       </c>
       <c r="I686" s="5" t="n">
-        <v>21615</v>
+        <v>23488</v>
       </c>
       <c r="J686" s="3" t="inlineStr">
         <is>
@@ -44480,10 +44482,10 @@
         </is>
       </c>
       <c r="K686" s="5" t="n">
-        <v>14006800</v>
+        <v>15243400</v>
       </c>
       <c r="L686" s="5" t="n">
-        <v>21615</v>
+        <v>23488</v>
       </c>
       <c r="M686" s="3" t="inlineStr">
         <is>
@@ -44499,7 +44501,7 @@
     <row r="687">
       <c r="A687" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B687" s="3" t="inlineStr">
@@ -44527,14 +44529,14 @@
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H687" s="5" t="n">
-        <v>13909300</v>
+        <v>6223500</v>
       </c>
       <c r="I687" s="5" t="n">
-        <v>45905</v>
+        <v>20540</v>
       </c>
       <c r="J687" s="3" t="inlineStr">
         <is>
@@ -44542,10 +44544,10 @@
         </is>
       </c>
       <c r="K687" s="5" t="n">
-        <v>13909300</v>
+        <v>6223500</v>
       </c>
       <c r="L687" s="5" t="n">
-        <v>45905</v>
+        <v>20540</v>
       </c>
       <c r="M687" s="3" t="inlineStr">
         <is>
@@ -44561,7 +44563,7 @@
     <row r="688">
       <c r="A688" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B688" s="3" t="inlineStr">
@@ -44580,7 +44582,7 @@
         </is>
       </c>
       <c r="E688" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F688" s="3" t="inlineStr">
         <is>
@@ -44589,14 +44591,14 @@
       </c>
       <c r="G688" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="H688" s="5" t="n">
-        <v>6109200</v>
+        <v>6624000</v>
       </c>
       <c r="I688" s="5" t="n">
-        <v>20096</v>
+        <v>21861</v>
       </c>
       <c r="J688" s="3" t="inlineStr">
         <is>
@@ -44604,10 +44606,10 @@
         </is>
       </c>
       <c r="K688" s="5" t="n">
-        <v>6109200</v>
+        <v>6624000</v>
       </c>
       <c r="L688" s="5" t="n">
-        <v>20096</v>
+        <v>21861</v>
       </c>
       <c r="M688" s="3" t="inlineStr">
         <is>
@@ -44623,7 +44625,7 @@
     <row r="689">
       <c r="A689" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B689" s="3" t="inlineStr">
@@ -44651,14 +44653,14 @@
       </c>
       <c r="G689" s="3" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H689" s="5" t="n">
-        <v>13909300</v>
+        <v>14621700</v>
       </c>
       <c r="I689" s="5" t="n">
-        <v>21432</v>
+        <v>22530</v>
       </c>
       <c r="J689" s="3" t="inlineStr">
         <is>
@@ -44666,10 +44668,10 @@
         </is>
       </c>
       <c r="K689" s="5" t="n">
-        <v>13909300</v>
+        <v>14621700</v>
       </c>
       <c r="L689" s="5" t="n">
-        <v>21432</v>
+        <v>22530</v>
       </c>
       <c r="M689" s="3" t="inlineStr">
         <is>
@@ -44685,7 +44687,7 @@
     <row r="690">
       <c r="A690" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B690" s="3" t="inlineStr">
@@ -44704,7 +44706,7 @@
         </is>
       </c>
       <c r="E690" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F690" s="3" t="inlineStr">
         <is>
@@ -44713,14 +44715,14 @@
       </c>
       <c r="G690" s="3" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H690" s="5" t="n">
-        <v>13808300</v>
+        <v>14810100</v>
       </c>
       <c r="I690" s="5" t="n">
-        <v>21309</v>
+        <v>22820</v>
       </c>
       <c r="J690" s="3" t="inlineStr">
         <is>
@@ -44728,10 +44730,10 @@
         </is>
       </c>
       <c r="K690" s="5" t="n">
-        <v>13808300</v>
+        <v>14810100</v>
       </c>
       <c r="L690" s="5" t="n">
-        <v>21309</v>
+        <v>22820</v>
       </c>
       <c r="M690" s="3" t="inlineStr">
         <is>
@@ -44747,7 +44749,7 @@
     <row r="691">
       <c r="A691" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B691" s="3" t="inlineStr">
@@ -44766,7 +44768,7 @@
         </is>
       </c>
       <c r="E691" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F691" s="3" t="inlineStr">
         <is>
@@ -44775,14 +44777,14 @@
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="H691" s="5" t="n">
-        <v>6108300</v>
+        <v>6185700</v>
       </c>
       <c r="I691" s="5" t="n">
-        <v>20093</v>
+        <v>20415</v>
       </c>
       <c r="J691" s="3" t="inlineStr">
         <is>
@@ -44790,10 +44792,10 @@
         </is>
       </c>
       <c r="K691" s="5" t="n">
-        <v>6108300</v>
+        <v>6185700</v>
       </c>
       <c r="L691" s="5" t="n">
-        <v>20093</v>
+        <v>20415</v>
       </c>
       <c r="M691" s="3" t="inlineStr">
         <is>
@@ -44809,7 +44811,7 @@
     <row r="692">
       <c r="A692" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B692" s="3" t="inlineStr">
@@ -44828,7 +44830,7 @@
         </is>
       </c>
       <c r="E692" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F692" s="3" t="inlineStr">
         <is>
@@ -44837,14 +44839,14 @@
       </c>
       <c r="G692" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H692" s="5" t="n">
-        <v>6173500</v>
+        <v>6199100</v>
       </c>
       <c r="I692" s="5" t="n">
-        <v>20308</v>
+        <v>20459</v>
       </c>
       <c r="J692" s="3" t="inlineStr">
         <is>
@@ -44852,10 +44854,10 @@
         </is>
       </c>
       <c r="K692" s="5" t="n">
-        <v>6173500</v>
+        <v>6199100</v>
       </c>
       <c r="L692" s="5" t="n">
-        <v>20308</v>
+        <v>20459</v>
       </c>
       <c r="M692" s="3" t="inlineStr">
         <is>
@@ -44871,7 +44873,7 @@
     <row r="693">
       <c r="A693" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B693" s="3" t="inlineStr">
@@ -44899,14 +44901,14 @@
       </c>
       <c r="G693" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H693" s="5" t="n">
-        <v>13901500</v>
+        <v>14446900</v>
       </c>
       <c r="I693" s="5" t="n">
-        <v>21420</v>
+        <v>22260</v>
       </c>
       <c r="J693" s="3" t="inlineStr">
         <is>
@@ -44914,10 +44916,10 @@
         </is>
       </c>
       <c r="K693" s="5" t="n">
-        <v>13901500</v>
+        <v>14446900</v>
       </c>
       <c r="L693" s="5" t="n">
-        <v>21420</v>
+        <v>22260</v>
       </c>
       <c r="M693" s="3" t="inlineStr">
         <is>
@@ -44933,7 +44935,7 @@
     <row r="694">
       <c r="A694" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B694" s="3" t="inlineStr">
@@ -44961,14 +44963,14 @@
       </c>
       <c r="G694" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H694" s="5" t="n">
-        <v>13801800</v>
+        <v>14395500</v>
       </c>
       <c r="I694" s="5" t="n">
-        <v>21299</v>
+        <v>22215</v>
       </c>
       <c r="J694" s="3" t="inlineStr">
         <is>
@@ -44976,10 +44978,10 @@
         </is>
       </c>
       <c r="K694" s="5" t="n">
-        <v>13801800</v>
+        <v>14395500</v>
       </c>
       <c r="L694" s="5" t="n">
-        <v>21299</v>
+        <v>22215</v>
       </c>
       <c r="M694" s="3" t="inlineStr">
         <is>
@@ -44995,7 +44997,7 @@
     <row r="695">
       <c r="A695" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B695" s="3" t="inlineStr">
@@ -45027,10 +45029,10 @@
         </is>
       </c>
       <c r="H695" s="5" t="n">
-        <v>6071400</v>
+        <v>6147900</v>
       </c>
       <c r="I695" s="5" t="n">
-        <v>19972</v>
+        <v>20223</v>
       </c>
       <c r="J695" s="3" t="inlineStr">
         <is>
@@ -45038,10 +45040,10 @@
         </is>
       </c>
       <c r="K695" s="5" t="n">
-        <v>6071400</v>
+        <v>6147900</v>
       </c>
       <c r="L695" s="5" t="n">
-        <v>19972</v>
+        <v>20223</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -45057,7 +45059,7 @@
     <row r="696">
       <c r="A696" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B696" s="3" t="inlineStr">
@@ -45076,7 +45078,7 @@
         </is>
       </c>
       <c r="E696" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F696" s="3" t="inlineStr">
         <is>
@@ -45085,14 +45087,14 @@
       </c>
       <c r="G696" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H696" s="5" t="n">
-        <v>6102400</v>
+        <v>6061500</v>
       </c>
       <c r="I696" s="5" t="n">
-        <v>20074</v>
+        <v>20005</v>
       </c>
       <c r="J696" s="3" t="inlineStr">
         <is>
@@ -45100,10 +45102,10 @@
         </is>
       </c>
       <c r="K696" s="5" t="n">
-        <v>6102400</v>
+        <v>6061500</v>
       </c>
       <c r="L696" s="5" t="n">
-        <v>20074</v>
+        <v>20005</v>
       </c>
       <c r="M696" s="3" t="inlineStr">
         <is>
@@ -45119,7 +45121,7 @@
     <row r="697">
       <c r="A697" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B697" s="3" t="inlineStr">
@@ -45147,14 +45149,14 @@
       </c>
       <c r="G697" s="3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H697" s="5" t="n">
-        <v>13591800</v>
+        <v>14428100</v>
       </c>
       <c r="I697" s="5" t="n">
-        <v>20975</v>
+        <v>22266</v>
       </c>
       <c r="J697" s="3" t="inlineStr">
         <is>
@@ -45162,10 +45164,10 @@
         </is>
       </c>
       <c r="K697" s="5" t="n">
-        <v>13591800</v>
+        <v>14428100</v>
       </c>
       <c r="L697" s="5" t="n">
-        <v>20975</v>
+        <v>22266</v>
       </c>
       <c r="M697" s="3" t="inlineStr">
         <is>
@@ -45181,7 +45183,7 @@
     <row r="698">
       <c r="A698" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B698" s="3" t="inlineStr">
@@ -45209,14 +45211,14 @@
       </c>
       <c r="G698" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="H698" s="5" t="n">
-        <v>13720400</v>
+        <v>14223600</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>21141</v>
+        <v>21916</v>
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
@@ -45224,10 +45226,10 @@
         </is>
       </c>
       <c r="K698" s="5" t="n">
-        <v>13720400</v>
+        <v>14223600</v>
       </c>
       <c r="L698" s="5" t="n">
-        <v>21141</v>
+        <v>21916</v>
       </c>
       <c r="M698" s="3" t="inlineStr">
         <is>
@@ -45243,7 +45245,7 @@
     <row r="699">
       <c r="A699" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B699" s="3" t="inlineStr">
@@ -45271,14 +45273,14 @@
       </c>
       <c r="G699" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H699" s="5" t="n">
-        <v>6719200</v>
+        <v>6581500</v>
       </c>
       <c r="I699" s="5" t="n">
-        <v>23827</v>
+        <v>23339</v>
       </c>
       <c r="J699" s="3" t="inlineStr">
         <is>
@@ -45286,10 +45288,10 @@
         </is>
       </c>
       <c r="K699" s="5" t="n">
-        <v>6719200</v>
+        <v>6581500</v>
       </c>
       <c r="L699" s="5" t="n">
-        <v>23827</v>
+        <v>23339</v>
       </c>
       <c r="M699" s="3" t="inlineStr">
         <is>
@@ -45305,7 +45307,7 @@
     <row r="700">
       <c r="A700" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B700" s="3" t="inlineStr">
@@ -45333,14 +45335,14 @@
       </c>
       <c r="G700" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H700" s="5" t="n">
-        <v>6608100</v>
+        <v>6560100</v>
       </c>
       <c r="I700" s="5" t="n">
-        <v>23433</v>
+        <v>23263</v>
       </c>
       <c r="J700" s="3" t="inlineStr">
         <is>
@@ -45348,10 +45350,10 @@
         </is>
       </c>
       <c r="K700" s="5" t="n">
-        <v>6608100</v>
+        <v>6560100</v>
       </c>
       <c r="L700" s="5" t="n">
-        <v>23433</v>
+        <v>23263</v>
       </c>
       <c r="M700" s="3" t="inlineStr">
         <is>
@@ -45367,7 +45369,7 @@
     <row r="701">
       <c r="A701" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B701" s="3" t="inlineStr">
@@ -45386,7 +45388,7 @@
         </is>
       </c>
       <c r="E701" s="4" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
@@ -45395,14 +45397,14 @@
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
-        <v>16854300</v>
+        <v>17241300</v>
       </c>
       <c r="I701" s="5" t="n">
-        <v>26924</v>
+        <v>27498</v>
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
@@ -45410,10 +45412,10 @@
         </is>
       </c>
       <c r="K701" s="5" t="n">
-        <v>16854300</v>
+        <v>17241300</v>
       </c>
       <c r="L701" s="5" t="n">
-        <v>26924</v>
+        <v>27498</v>
       </c>
       <c r="M701" s="3" t="inlineStr">
         <is>
@@ -45429,7 +45431,7 @@
     <row r="702">
       <c r="A702" s="3" t="inlineStr">
         <is>
-          <t>低座D座</t>
+          <t>低座B座</t>
         </is>
       </c>
       <c r="B702" s="3" t="inlineStr">
@@ -45457,32 +45459,2512 @@
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="H702" s="5" t="n">
+        <v>17109900</v>
+      </c>
+      <c r="I702" s="5" t="n">
+        <v>27289</v>
+      </c>
+      <c r="J702" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K702" s="5" t="n">
+        <v>17109900</v>
+      </c>
+      <c r="L702" s="5" t="n">
+        <v>27289</v>
+      </c>
+      <c r="M702" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N702" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C703" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D703" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E703" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F703" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G703" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H703" s="5" t="n">
+        <v>6637500</v>
+      </c>
+      <c r="I703" s="5" t="n">
+        <v>21834</v>
+      </c>
+      <c r="J703" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K703" s="5" t="n">
+        <v>6637500</v>
+      </c>
+      <c r="L703" s="5" t="n">
+        <v>21834</v>
+      </c>
+      <c r="M703" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N703" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B704" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C704" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D704" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E704" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F704" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G704" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H704" s="5" t="n">
+        <v>6566400</v>
+      </c>
+      <c r="I704" s="5" t="n">
+        <v>21671</v>
+      </c>
+      <c r="J704" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K704" s="5" t="n">
+        <v>6566400</v>
+      </c>
+      <c r="L704" s="5" t="n">
+        <v>21671</v>
+      </c>
+      <c r="M704" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N704" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C705" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D705" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E705" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F705" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G705" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H705" s="5" t="n">
+        <v>14935500</v>
+      </c>
+      <c r="I705" s="5" t="n">
+        <v>23049</v>
+      </c>
+      <c r="J705" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K705" s="5" t="n">
+        <v>14935500</v>
+      </c>
+      <c r="L705" s="5" t="n">
+        <v>23049</v>
+      </c>
+      <c r="M705" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N705" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C706" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D706" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E706" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F706" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G706" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="H706" s="5" t="n">
+        <v>15207000</v>
+      </c>
+      <c r="I706" s="5" t="n">
+        <v>23468</v>
+      </c>
+      <c r="J706" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K706" s="5" t="n">
+        <v>15207000</v>
+      </c>
+      <c r="L706" s="5" t="n">
+        <v>23468</v>
+      </c>
+      <c r="M706" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N706" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C707" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D707" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E707" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F707" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G707" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H707" s="5" t="n">
+        <v>6597900</v>
+      </c>
+      <c r="I707" s="5" t="n">
+        <v>21775</v>
+      </c>
+      <c r="J707" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K707" s="5" t="n">
+        <v>6597900</v>
+      </c>
+      <c r="L707" s="5" t="n">
+        <v>21775</v>
+      </c>
+      <c r="M707" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N707" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C708" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D708" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E708" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F708" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G708" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H708" s="5" t="n">
+        <v>6599300</v>
+      </c>
+      <c r="I708" s="5" t="n">
+        <v>21708</v>
+      </c>
+      <c r="J708" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K708" s="5" t="n">
+        <v>6599300</v>
+      </c>
+      <c r="L708" s="5" t="n">
+        <v>21708</v>
+      </c>
+      <c r="M708" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N708" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C709" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D709" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E709" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F709" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G709" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="H709" s="5" t="n">
+        <v>14803200</v>
+      </c>
+      <c r="I709" s="5" t="n">
+        <v>22809</v>
+      </c>
+      <c r="J709" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K709" s="5" t="n">
+        <v>14803200</v>
+      </c>
+      <c r="L709" s="5" t="n">
+        <v>22809</v>
+      </c>
+      <c r="M709" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N709" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C710" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D710" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E710" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F710" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G710" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H710" s="5" t="n">
+        <v>14907600</v>
+      </c>
+      <c r="I710" s="5" t="n">
+        <v>23006</v>
+      </c>
+      <c r="J710" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K710" s="5" t="n">
+        <v>14907600</v>
+      </c>
+      <c r="L710" s="5" t="n">
+        <v>23006</v>
+      </c>
+      <c r="M710" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N710" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C711" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D711" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E711" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F711" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G711" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H711" s="5" t="n">
+        <v>6741400</v>
+      </c>
+      <c r="I711" s="5" t="n">
+        <v>22176</v>
+      </c>
+      <c r="J711" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K711" s="5" t="n">
+        <v>6741400</v>
+      </c>
+      <c r="L711" s="5" t="n">
+        <v>22176</v>
+      </c>
+      <c r="M711" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N711" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B712" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C712" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D712" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E712" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F712" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G712" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H712" s="5" t="n">
+        <v>6596200</v>
+      </c>
+      <c r="I712" s="5" t="n">
+        <v>21698</v>
+      </c>
+      <c r="J712" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K712" s="5" t="n">
+        <v>6596200</v>
+      </c>
+      <c r="L712" s="5" t="n">
+        <v>21698</v>
+      </c>
+      <c r="M712" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N712" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C713" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D713" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E713" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F713" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G713" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="H713" s="5" t="n">
+        <v>14715000</v>
+      </c>
+      <c r="I713" s="5" t="n">
+        <v>22673</v>
+      </c>
+      <c r="J713" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K713" s="5" t="n">
+        <v>14715000</v>
+      </c>
+      <c r="L713" s="5" t="n">
+        <v>22673</v>
+      </c>
+      <c r="M713" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N713" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B714" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C714" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D714" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E714" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F714" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G714" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="H714" s="5" t="n">
+        <v>14820300</v>
+      </c>
+      <c r="I714" s="5" t="n">
+        <v>22836</v>
+      </c>
+      <c r="J714" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K714" s="5" t="n">
+        <v>14820300</v>
+      </c>
+      <c r="L714" s="5" t="n">
+        <v>22836</v>
+      </c>
+      <c r="M714" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N714" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B715" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C715" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D715" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E715" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F715" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G715" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="H715" s="5" t="n">
+        <v>6519600</v>
+      </c>
+      <c r="I715" s="5" t="n">
+        <v>21446</v>
+      </c>
+      <c r="J715" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K715" s="5" t="n">
+        <v>6519600</v>
+      </c>
+      <c r="L715" s="5" t="n">
+        <v>21446</v>
+      </c>
+      <c r="M715" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N715" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C716" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D716" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E716" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F716" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G716" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="H716" s="5" t="n">
+        <v>6448500</v>
+      </c>
+      <c r="I716" s="5" t="n">
+        <v>21212</v>
+      </c>
+      <c r="J716" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K716" s="5" t="n">
+        <v>6448500</v>
+      </c>
+      <c r="L716" s="5" t="n">
+        <v>21212</v>
+      </c>
+      <c r="M716" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N716" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B717" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C717" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D717" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E717" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F717" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G717" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="H717" s="5" t="n">
+        <v>14789300</v>
+      </c>
+      <c r="I717" s="5" t="n">
+        <v>22788</v>
+      </c>
+      <c r="J717" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K717" s="5" t="n">
+        <v>14789300</v>
+      </c>
+      <c r="L717" s="5" t="n">
+        <v>22788</v>
+      </c>
+      <c r="M717" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N717" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C718" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D718" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E718" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F718" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G718" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H718" s="5" t="n">
+        <v>14732100</v>
+      </c>
+      <c r="I718" s="5" t="n">
+        <v>22700</v>
+      </c>
+      <c r="J718" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K718" s="5" t="n">
+        <v>14732100</v>
+      </c>
+      <c r="L718" s="5" t="n">
+        <v>22700</v>
+      </c>
+      <c r="M718" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N718" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D719" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E719" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F719" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G719" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="H719" s="5" t="n">
+        <v>6885000</v>
+      </c>
+      <c r="I719" s="5" t="n">
+        <v>24415</v>
+      </c>
+      <c r="J719" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K719" s="5" t="n">
+        <v>6885000</v>
+      </c>
+      <c r="L719" s="5" t="n">
+        <v>24415</v>
+      </c>
+      <c r="M719" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N719" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C720" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D720" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E720" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F720" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G720" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="H720" s="5" t="n">
+        <v>6809400</v>
+      </c>
+      <c r="I720" s="5" t="n">
+        <v>24147</v>
+      </c>
+      <c r="J720" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K720" s="5" t="n">
+        <v>6809400</v>
+      </c>
+      <c r="L720" s="5" t="n">
+        <v>24147</v>
+      </c>
+      <c r="M720" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N720" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B721" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C721" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D721" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E721" s="4" t="n">
+        <v>627</v>
+      </c>
+      <c r="F721" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G721" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H721" s="5" t="n">
+        <v>17827800</v>
+      </c>
+      <c r="I721" s="5" t="n">
+        <v>28433</v>
+      </c>
+      <c r="J721" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K721" s="5" t="n">
+        <v>17827800</v>
+      </c>
+      <c r="L721" s="5" t="n">
+        <v>28433</v>
+      </c>
+      <c r="M721" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N721" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="3" t="inlineStr">
+        <is>
+          <t>低座C座</t>
+        </is>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C722" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D722" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E722" s="4" t="n">
+        <v>627</v>
+      </c>
+      <c r="F722" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G722" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="H722" s="5" t="n">
+        <v>17585100</v>
+      </c>
+      <c r="I722" s="5" t="n">
+        <v>28046</v>
+      </c>
+      <c r="J722" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K722" s="5" t="n">
+        <v>17585100</v>
+      </c>
+      <c r="L722" s="5" t="n">
+        <v>28046</v>
+      </c>
+      <c r="M722" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N722" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D723" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E723" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F723" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G723" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H723" s="5" t="n">
+        <v>6284200</v>
+      </c>
+      <c r="I723" s="5" t="n">
+        <v>20740</v>
+      </c>
+      <c r="J723" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K723" s="5" t="n">
+        <v>6284200</v>
+      </c>
+      <c r="L723" s="5" t="n">
+        <v>20740</v>
+      </c>
+      <c r="M723" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N723" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C724" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D724" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E724" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F724" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G724" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H724" s="5" t="n">
+        <v>6248500</v>
+      </c>
+      <c r="I724" s="5" t="n">
+        <v>20622</v>
+      </c>
+      <c r="J724" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K724" s="5" t="n">
+        <v>6248500</v>
+      </c>
+      <c r="L724" s="5" t="n">
+        <v>20622</v>
+      </c>
+      <c r="M724" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N724" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D725" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E725" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F725" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G725" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="H725" s="5" t="n">
+        <v>13879800</v>
+      </c>
+      <c r="I725" s="5" t="n">
+        <v>21386</v>
+      </c>
+      <c r="J725" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K725" s="5" t="n">
+        <v>13879800</v>
+      </c>
+      <c r="L725" s="5" t="n">
+        <v>21386</v>
+      </c>
+      <c r="M725" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N725" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C726" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D726" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E726" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F726" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G726" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H726" s="5" t="n">
+        <v>14006800</v>
+      </c>
+      <c r="I726" s="5" t="n">
+        <v>21615</v>
+      </c>
+      <c r="J726" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K726" s="5" t="n">
+        <v>14006800</v>
+      </c>
+      <c r="L726" s="5" t="n">
+        <v>21615</v>
+      </c>
+      <c r="M726" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N726" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B727" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D727" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E727" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="F727" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G727" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="H727" s="5" t="n">
+        <v>13909300</v>
+      </c>
+      <c r="I727" s="5" t="n">
+        <v>45905</v>
+      </c>
+      <c r="J727" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K727" s="5" t="n">
+        <v>13909300</v>
+      </c>
+      <c r="L727" s="5" t="n">
+        <v>45905</v>
+      </c>
+      <c r="M727" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N727" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B728" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C728" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D728" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E728" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F728" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G728" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H728" s="5" t="n">
+        <v>6109200</v>
+      </c>
+      <c r="I728" s="5" t="n">
+        <v>20096</v>
+      </c>
+      <c r="J728" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K728" s="5" t="n">
+        <v>6109200</v>
+      </c>
+      <c r="L728" s="5" t="n">
+        <v>20096</v>
+      </c>
+      <c r="M728" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N728" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C729" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D729" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E729" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F729" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G729" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="H729" s="5" t="n">
+        <v>13909300</v>
+      </c>
+      <c r="I729" s="5" t="n">
+        <v>21432</v>
+      </c>
+      <c r="J729" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K729" s="5" t="n">
+        <v>13909300</v>
+      </c>
+      <c r="L729" s="5" t="n">
+        <v>21432</v>
+      </c>
+      <c r="M729" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N729" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B730" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C730" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D730" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E730" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F730" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G730" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="H730" s="5" t="n">
+        <v>13808300</v>
+      </c>
+      <c r="I730" s="5" t="n">
+        <v>21309</v>
+      </c>
+      <c r="J730" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K730" s="5" t="n">
+        <v>13808300</v>
+      </c>
+      <c r="L730" s="5" t="n">
+        <v>21309</v>
+      </c>
+      <c r="M730" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N730" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D731" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E731" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F731" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G731" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-26</t>
+        </is>
+      </c>
+      <c r="H731" s="5" t="n">
+        <v>6108300</v>
+      </c>
+      <c r="I731" s="5" t="n">
+        <v>20093</v>
+      </c>
+      <c r="J731" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K731" s="5" t="n">
+        <v>6108300</v>
+      </c>
+      <c r="L731" s="5" t="n">
+        <v>20093</v>
+      </c>
+      <c r="M731" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N731" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B732" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C732" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D732" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E732" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F732" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G732" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H732" s="5" t="n">
+        <v>6173500</v>
+      </c>
+      <c r="I732" s="5" t="n">
+        <v>20308</v>
+      </c>
+      <c r="J732" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K732" s="5" t="n">
+        <v>6173500</v>
+      </c>
+      <c r="L732" s="5" t="n">
+        <v>20308</v>
+      </c>
+      <c r="M732" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N732" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C733" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D733" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E733" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F733" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G733" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H733" s="5" t="n">
+        <v>13901500</v>
+      </c>
+      <c r="I733" s="5" t="n">
+        <v>21420</v>
+      </c>
+      <c r="J733" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K733" s="5" t="n">
+        <v>13901500</v>
+      </c>
+      <c r="L733" s="5" t="n">
+        <v>21420</v>
+      </c>
+      <c r="M733" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N733" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C734" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D734" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E734" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F734" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G734" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H734" s="5" t="n">
+        <v>13801800</v>
+      </c>
+      <c r="I734" s="5" t="n">
+        <v>21299</v>
+      </c>
+      <c r="J734" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K734" s="5" t="n">
+        <v>13801800</v>
+      </c>
+      <c r="L734" s="5" t="n">
+        <v>21299</v>
+      </c>
+      <c r="M734" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N734" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C735" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D735" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E735" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F735" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G735" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="H735" s="5" t="n">
+        <v>6071400</v>
+      </c>
+      <c r="I735" s="5" t="n">
+        <v>19972</v>
+      </c>
+      <c r="J735" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K735" s="5" t="n">
+        <v>6071400</v>
+      </c>
+      <c r="L735" s="5" t="n">
+        <v>19972</v>
+      </c>
+      <c r="M735" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N735" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B736" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C736" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D736" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E736" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="F736" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G736" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H736" s="5" t="n">
+        <v>6102400</v>
+      </c>
+      <c r="I736" s="5" t="n">
+        <v>20074</v>
+      </c>
+      <c r="J736" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K736" s="5" t="n">
+        <v>6102400</v>
+      </c>
+      <c r="L736" s="5" t="n">
+        <v>20074</v>
+      </c>
+      <c r="M736" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N736" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B737" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C737" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D737" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E737" s="4" t="n">
+        <v>648</v>
+      </c>
+      <c r="F737" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G737" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="H737" s="5" t="n">
+        <v>13591800</v>
+      </c>
+      <c r="I737" s="5" t="n">
+        <v>20975</v>
+      </c>
+      <c r="J737" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K737" s="5" t="n">
+        <v>13591800</v>
+      </c>
+      <c r="L737" s="5" t="n">
+        <v>20975</v>
+      </c>
+      <c r="M737" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N737" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B738" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C738" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D738" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E738" s="4" t="n">
+        <v>649</v>
+      </c>
+      <c r="F738" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G738" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="H738" s="5" t="n">
+        <v>13720400</v>
+      </c>
+      <c r="I738" s="5" t="n">
+        <v>21141</v>
+      </c>
+      <c r="J738" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K738" s="5" t="n">
+        <v>13720400</v>
+      </c>
+      <c r="L738" s="5" t="n">
+        <v>21141</v>
+      </c>
+      <c r="M738" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N738" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C739" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D739" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E739" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F739" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G739" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H739" s="5" t="n">
+        <v>6719200</v>
+      </c>
+      <c r="I739" s="5" t="n">
+        <v>23827</v>
+      </c>
+      <c r="J739" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K739" s="5" t="n">
+        <v>6719200</v>
+      </c>
+      <c r="L739" s="5" t="n">
+        <v>23827</v>
+      </c>
+      <c r="M739" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N739" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C740" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D740" s="3" t="inlineStr">
+        <is>
+          <t>1房</t>
+        </is>
+      </c>
+      <c r="E740" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="F740" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G740" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H740" s="5" t="n">
+        <v>6608100</v>
+      </c>
+      <c r="I740" s="5" t="n">
+        <v>23433</v>
+      </c>
+      <c r="J740" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K740" s="5" t="n">
+        <v>6608100</v>
+      </c>
+      <c r="L740" s="5" t="n">
+        <v>23433</v>
+      </c>
+      <c r="M740" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N740" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B741" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D741" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E741" s="4" t="n">
+        <v>626</v>
+      </c>
+      <c r="F741" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G741" s="3" t="inlineStr">
+        <is>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="H741" s="5" t="n">
+        <v>16854300</v>
+      </c>
+      <c r="I741" s="5" t="n">
+        <v>26924</v>
+      </c>
+      <c r="J741" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K741" s="5" t="n">
+        <v>16854300</v>
+      </c>
+      <c r="L741" s="5" t="n">
+        <v>26924</v>
+      </c>
+      <c r="M741" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N741" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="3" t="inlineStr">
+        <is>
+          <t>低座D座</t>
+        </is>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C742" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D742" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E742" s="4" t="n">
+        <v>627</v>
+      </c>
+      <c r="F742" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G742" s="3" t="inlineStr">
+        <is>
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="H702" s="5" t="n">
+      <c r="H742" s="5" t="n">
         <v>16816700</v>
       </c>
-      <c r="I702" s="5" t="n">
+      <c r="I742" s="5" t="n">
         <v>26821</v>
       </c>
-      <c r="J702" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K702" s="5" t="n">
+      <c r="J742" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K742" s="5" t="n">
         <v>16816700</v>
       </c>
-      <c r="L702" s="5" t="n">
+      <c r="L742" s="5" t="n">
         <v>26821</v>
       </c>
-      <c r="M702" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N702" s="3" t="inlineStr">
+      <c r="M742" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N742" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -51863,6 +54345,642 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
+          <t>低座B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1524万
+$23,488/呎
+(23年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1497万
+$23,069/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$617万
+$20,361/呎
+(23年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$626万
+$20,664/呎
+(23年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1481万
+$22,820/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1462万
+$22,530/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$662万
+$21,861/呎
+(23年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$622万
+$20,540/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1440万
+$22,215/呎
+(23年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1445万
+$22,260/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$620万
+$20,459/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$619万
+$20,415/呎
+(23年-07月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1422万
+$21,916/呎
+(23年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 648呎 (3房)
+$1443万
+$22,266/呎
+(23年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$606万
+$20,005/呎
+(23年-07月-25日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$615万
+$20,223/呎
+(23年-07月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1711万
+$27,289/呎
+(23年-07月-25日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 627呎 (3房)
+$1724万
+$27,498/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$656万
+$23,263/呎
+(23年-07月-26日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$658万
+$23,339/呎
+(23年-07月-25日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1521万
+$23,468/呎
+(23年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 648呎 (3房)
+$1494万
+$23,049/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 303呎 (1房)
+$657万
+$21,671/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$664万
+$21,834/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 648呎 (3房)
+$1491万
+$23,006/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1480万
+$22,809/呎
+(23年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$660万
+$21,708/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 303呎 (1房)
+$660万
+$21,775/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1482万
+$22,836/呎
+(23年-08月-01日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1472万
+$22,673/呎
+(23年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$660万
+$21,698/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$674万
+$22,176/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 649呎 (3房)
+$1473万
+$22,700/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 649呎 (3房)
+$1479万
+$22,788/呎
+(23年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 304呎 (1房)
+$645万
+$21,212/呎
+(23年-08月-07日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 304呎 (1房)
+$652万
+$21,446/呎
+(23年-07月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 627呎 (3房)
+$1759万
+$28,046/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 627呎 (3房)
+$1783万
+$28,433/呎
+(23年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 282呎 (1房)
+$681万
+$24,147/呎
+(23年-08月-01日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 282呎 (1房)
+$688万
+$24,415/呎
+(23年-07月-31日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
           <t>低座D座 销控网格图</t>
         </is>
       </c>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>31014000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>33099</v>
+        <v>33135</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>31014000</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>33099</v>
+        <v>33135</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -50205,9 +50205,9 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3101万
-$33,099/呎
+$33,135/呎
 (26年-08月-14日)</t>
         </is>
       </c>
